--- a/Input/File_086.xlsx
+++ b/Input/File_086.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5005" uniqueCount="5005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4849" uniqueCount="4849">
   <si>
     <t>链接</t>
   </si>
@@ -44,69 +44,18 @@
     <t>Screenshots</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:E166F9441A3CD62C0C5C0CC020677D0D1A2E3403</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3C3B9CECF1ED52CE192FEEF769F5F61C76996DA9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:D8D9F3598C0317DDB9C4D3A8B2D8C8351B0D2C27</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:783567BDB5F450E1343924645FEBFBB86D1BAF86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:783089F1BFA543C3463D9D3CFD37030A61614C1D</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:16B4F125332ED0BFCB5ECF08159B96EC0C51299C</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:B7D18B37E9114646780CEB2DAFE10E02FC5B08DB</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:D551136FFBC56239208E7D2462054B6084BC070A</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:AA602B892542739AFBECC8E1EC922E0DD4D13E69</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3E80F6D79E4933A7E71CC940ACD1EFA5C9D7C433</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4BF2DEA26514B936F5C7FB6432FE30A5162AF2A2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2B352DC943F8038C4A900108A0CCBF68F9CE6139</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9BA041A8710F3FE936EC8547320F651D5F4EBDBE</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:DD197D777FB907FDE6DC5A1DB38E268FC8C75BCC</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:C553CD69A2380AACC4DF82A2D4BC5939C51C11B4</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:1C6AEC150B92C67AF427193353519434D285FC4F</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:4538101D3E633C01541097009ACAA4A30B84026D</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:345347B319ACA3A657FF0BEC00FDD2C8BC89B28C</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:5148C6D32325A3860CCC564F07C1E4323D76A1D5</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:E21B0CDA358DBEEE0CE53914115DB1AAC01DAEFA</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9989650758FFA7B6B6E2E7CD2EB69F3B9DBF1718</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:DFD233E988F043F395593ADA4D69DB83014BA520</t>
   </si>
   <si>
@@ -119,21 +68,9 @@
     <t>magnet:?xt=urn:btih:CFE220FF42A134952265D817E1DAEE42B18CFB29</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:4A3F7BD59B613EC55531B5FCF5AC5EE736955A9E</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:F8849CE7704EAD17A5C85E921A9E4CB4DC7F7495</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:8AAEB80A0A8BEE745F802431377ED125831E770C</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:289CFFAEC7D5F1B567889980EF14663F4B64F195</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:69CBC374807C44EA974BE1834217996A9275C5A2</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:E7446FE838AB1CDF9EF07E88F46E14FDC138E348</t>
   </si>
   <si>
@@ -149,81 +86,21 @@
     <t>magnet:?xt=urn:btih:D14CDE5782C1A3CB4DFFFD0B8F459C73724603AA</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:7D91853830AF8269CD830EC9B00F78FB71A22EB1</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:38900DABD8157F7251C3ECE579826D59B58B1882</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:42C3643341F9F5B9D2257460CA97974BE843BAB5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6BB3788C94CD222A8693187B4F4C913A2F502574</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:67A976BB02F9FE1AD34F987C969E44552328CC96</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:43A93922647944DC5FF33915DCA0F17B07A451FE</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:EBC0CEFB8E8C2CC8BFE499F0BBD881FDCD317ED6</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:86A6D8107A21394D2F21F4C2565B98171A227B0E</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:030B44A0750059F1BD4938C2A16C2315D59783E8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3FF75A8E483D61C6EA1CFE233C16C27E729C6FFA</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:75ABF5917F8E9DC4E82060A600E619F7B853F96B</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C03C123EE0C712028B996A1C82FA99BA4586DD38</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:F5F4BD042AA4E8EA3C2226812F39BDE825565A32</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:30C2149D329BA67001F20B565552D71CA5596B08</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:84ADFED135586A4F395510D970FD9B481040BC7B</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:EE88827AFA5A4694957D01DDE21B985C692B1C60</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1BF69EB61D19AFECDDD8AC8DF7AD87AC35F88673</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:E3BE008E7CF5786122DD154294FE43C505064974</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:B90BB424118C41C5F68E03F5A882E66EC09EE419</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7A7B440993F85769E4F20C8BB7C0B355071A531A</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:DB9901662D66C053BC86EB8291806A238A42E2E4</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:051E6E5BFE8AE1DE964D3C86FE788AD21B4BE8DD</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4C91897B788E49E31057908860441989F72E5B26</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5F2B788DE92CF885AF56B4735AAA1576554E21BB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:D7AFB18257D22872B6D222E3EF0F57A718258097</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:8CD7895B0BE44EE399A4AC65B0B57909732CDEDA</t>
   </si>
   <si>
@@ -239,63 +116,21 @@
     <t>magnet:?xt=urn:btih:E9CB1F037FA505B23673CC602C4BB958A15F3397</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:DE5F641B6FEBB24433A1EF59795CCF8AEB560389</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5DE27EBEB89B5E074736C8C053A663BF127F5200</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:5AABCAE6E9A7E0904B3C1AD14C8CDAA0ED0F6EBE</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:874DA5006916C508D482FB6929B50D8CBC7AA245</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:E30C216BA0DEEC8EDCBF8F4207874BD8475842F4</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:7DCF2724C96081A2F85C088665FB1267C233F25F</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:621AC3120F35944ED01EF282B747F10C58F17A09</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:EC73985FB2424DC5F96E49E0D765A31911F8ED47</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:01095CB78E4257C592D015E9DD2588CED45D87B7</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:99A49903D53F93DC7B34BFEF39C694BC63AA42BA</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:0E65311AD8E6DB01BE23FFC23BBEE6D245F2CE46</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5439617D4C29153D77CBFEA569BC03264A41EC57</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C6717F940435299A2FBB794A6D09979075695AB2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:55FAB356A30DEB03C27A109FB48C87D4B297C8B2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:009ACC623B90C17BB431E06254AE2B6D9ABA84DE</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:DC2DB5E1650255F20FD0032024E0C22C2280AD9D</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:2DC748FCA4EA4EFE29C33303DE289C95DE69343D</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:67772F326500A457C099AE0A4950BB55C7ECE974</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3C3474439B64FD2B77ED08AFC4275FFA5D73B0FA</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:E37D294EBA2EA53C4000A917F9302CDF48257027</t>
   </si>
   <si>
@@ -308,159 +143,48 @@
     <t>magnet:?xt=urn:btih:88608DD6A417C80E83DAF87B0539A9FE50588DD1</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:466C275D74450747CEEFC4624541F658EC0599E4</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:78B7E0C170C8EC8DCCEF3E8530EABC04A45932D4</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:B8B0F1C551BBDC1D377AE24E23607C36FABF3C7D</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:7872E8AFC435A8F654BCFDB0AF21EFEBF93736BF</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:967BEF0653FB480097FDB72A2E290CCD2DD9B0B7</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:A02F3C7291DFB884A263BC7F79AD23D416534319</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:95EAFE706CFA40402A318380E4AA415D2FD75087</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:18E01AC36CA2547920C8547B880AA5FC210D6C07</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:2BE57C633F85BE0D480032E4613DEA1F0801ADAD</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:62460098E3FA6125264B63003B67835209740726</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:0A5CB7810F81B6F8B8B08E49763DCEF0FE347539</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:659D0DADF97005AD81454CC30110B55920F2D542</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9FBD9B4479AAE2864768DCE22948C450FF854200</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:BA9FFEFF133E06497A92B001B61DD2A5ACAFACF8</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:9412EFDF0B0260A0718D17448E980DA526597D86</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:896C38342B9E69EDDBD69BE085B6E5F34D7F911E</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:F3CEEB83EE70EBE8252F632D6BAE8B2167032843</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:5911F5442C1C27CDCEE550FD8AF4E88F9A623B8B</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:09AF11ECE79C9AC2B1D513C0427054C88929A749</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0D61AC4C2D8B77C6EDAEDC37B06D346889BABAD5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C8DF21D95B3D0B963A56FB6D7696699A2B1D9290</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1EC108688AF399A2A7B320F9748D6D29E5E6BE81</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:1A02795961203B01218CE368C79BBC8E9CBA8C21</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:64F9E7F65A4A2566BCA682081392F9D0A05B1945</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:318F3774E6CA716AAD5B9E2FA53C9E6274FB7818</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:DF54F0D3F53C818FA377003FACC3F3AC1CAAC564</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:67DD1D3C9157C868FF2F89926E8678A2012E103A</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6F260C9B2019EF620A040186AC271BE78AE15671</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:BAA8E52C5F09AE56F6C3F1E2C38EECAF11B87369</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:F0AA19C71FF3D970BF41C9DB2EBE57AFA4431E33</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C1C40D5A41ED16CF9EF5183E238F051E245EA40F</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:9666839D81E9AF1E9CF302F63CF4E394DC2F9C5C</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:9D18351AEF06523D18E6496713CC17E1EBB58991</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:29C7263BF8E2EFE2FD262B989FF942A67897FBCD</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:CEBDFAE68508E0A0A6EE606EF97A0F9EE3755D84</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:173E6A9D5904D01EE8968E625864217FECD97CF4</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:2E8B886485277E96EF359550FE79FDB3CD08FF9C</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:87768C42F35AD4133A38829F55FF540B290EF8CD</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6959805FA2FB10D84A6B0C7C7727B42437CCF799</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:CD7E5D3497D21007B6C973101967985CF30A1DA6</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:F94B8C876AA8E713BA66F92EDD8A5DB43AFEB7A2</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:0F538FBD4805DB4B1FA77E95468F6993867E5A33</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:64D0CB8E2F7EF9D2D04AE0E86B4411C326B8FF20</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:99C4305EBA78257D4FC943A749B04A6E361DC40D</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:400BA8AF15A699DF6D3662FD456430E14904EB6E</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:71CEE6C424720C0ADF75713133D8E1EFA849C719</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:69577F5EB4F3162718534DA4BF726F73E6161334</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C34241FDBFF96F7F9B30DB0B4E823B3A5FC81ADB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:56566038BD950ABC48E9E5E96A1888D7B1F933BA</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:147175560080958727306103C7BDE2F0AC9F5CDE</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:1F49B5C6EC7F992CE24413930BBC523C72061921</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:72C03908A8F13A1824792E9DF274FE77C26D0211</t>
   </si>
   <si>
@@ -470,87 +194,27 @@
     <t>magnet:?xt=urn:btih:C3255A958E89AE7B38D7BD058B0A8E4084C3AA7C</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:B874ACD11CAD67B9CF01EA82456454FA93AD9E04</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2C86F9E57959FA436C3F38834B960D5FCA025AE3</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:251F1467D6694465C9A5FDD0361CA02B5C604679</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:FE780A0471BADCBAF9CBE6DE432224126EA2B2EA</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:A386EC10509CD16658F4F76A256D4324EB99F8F9</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:D425420C0D6E8C5B95EB42BFFD2C091E8D5FADC5</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:288314BB2FAB964D8360EB7A639B703C56053CC2</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:97AFAA78C308706F1E3D9D88D80358B97E27CFDA</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:69155849756FAF6F5F08B6F340AC63D40411BAFB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5AAF3A73639EE0BE25A4930F65924C2DA8BF926E</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:0F8E8B9B6EB65848CF312AEF16790719E693D465</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:DD36F0C6544067903BFE570A840BBBFE4CF6C7AE</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:F2CBC8BF1D4D44354345160BB6CCB7ADC78F45DA</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:736DE0AA583D17B0164FE50F365592563E8ED8F3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:AB55942AF0E26421BC0E7754B4271C5D3CCCCAC3</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:1F2CDC87C2F5CF98D02BDDD65B3A9BC3057CD3CC</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:AC583E396730711B5867CE523D156A1E9662DE74</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:F0D0A7A2A1C63688EED46399EB07243BCED795B2</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:1A4ECF90B31AC566AF9EF144303F265EC7A4BCC8</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:2FC42C87C486D820098834D99B5A620B7186A46C</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:010660D95DE9BF64DF56C53EE3B09450FF40B081</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C5C0BE14C1E0E3DCA5013499BDBE46D2E506FC78</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:A0005E7C2FBB082E40936D5502D4F7FE114F9457</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4218106B5FE7C8C67CF2E799A90D01F612CD111C</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:BBB5180DFDD1D1388C1413A0197D40931934374D</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:E380A6E44D47F75907101B763B8AD4C6A454515B</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:AA06B32F8EA3D8FE5B365A7C4767CE7105389BD7</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:E4EA7362C4959F1EC42F2FCFAD824E3B60238CCA</t>
   </si>
   <si>
@@ -566,36 +230,18 @@
     <t>magnet:?xt=urn:btih:988428C1DD3154C403946BA34D7059BF94EAE2DA</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:54C8329CAAA3FD89FB124AE8BDE9E9EDE877B32F</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:385F217FDA69DC7FD10E18490908AAAB768C7E2F</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:8083644315423265504C2F0ACFAB6BFACC3F2E58</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:55279A4952FEBD084C7724226D1406A759A7BB5D</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:6947B1F2B20CF03DFE484824F68C601E3A2D57A8</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:0BD838540E4A4F7C5FD742B0D49A966526571794</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:AA777797F0AD2B9723D90FC06E8E5509876A8035</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:5E392E920CE25E90A09BC8D9DB47E6ACC21207AE</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:33C10B30A4451D75148EE3F7844E53780134CBBE</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:CB747264A6926EF883257777F89F55D56520C85F</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:9C10D32CC71B7713BB7A08214EF17C2245D1CAC7</t>
   </si>
   <si>
@@ -608,9 +254,6 @@
     <t>magnet:?xt=urn:btih:468AED0D90CF4E3B0E20BF95513869C959D8EEF1</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:14972F0B3EC516D4197E5DEABE7865A60FE457E9</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:DB781EBB1EF507EC35C5A8A2BA1F33F5317D6BFD</t>
   </si>
   <si>
@@ -620,30 +263,9 @@
     <t>magnet:?xt=urn:btih:0ED18A1F24908B122C49BEB4BD8C747DE7F79FA6</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:6DAA7B5EE8FC5913E5C6D34D2CD2905B42327839</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:6E6956784E3443285E9E4832A9D3CA73C2ED584E</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:DD190690A66E2F159CCC06E8E9F3A6B39055233B</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:DA1B48F396958A8B68EFA63FD0F1097435866502</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8BAD2DDFC7611DEFFFEE25CE2E569774386303B6</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:DB66069875084F59D244E042A49D49A29A4DEB02</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:7E29CBEF316F6B1CE3B80A9B16767E7193B9A50B</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:5959109ADE9222A0AAA81AF1A624CA1D6F9C66CF</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:0259A888EEC68947D5733767130CF5349ED343B9</t>
   </si>
   <si>
@@ -653,54 +275,15 @@
     <t>magnet:?xt=urn:btih:F68137E9602C7E105ECEE7E8CC9A84C4CA605CD5</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:29083BFAC2BC042203F6CBF405C29ABA83834A0C</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:45928F684E02B71752F4757167D60BDEA51E8B37</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:22E279EE8BD775A286C16359368B0C3C07C51DBE</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:01B856D5E6AF009FB9C72CF70FB45795509D6808</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:EA995DC77FEE4F5A91FF6731639B887CED9396D4</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:0B326F5682843CD972028D2B7FE8CBD4A5E549CB</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:F50E53F4C51DA78F3FBCFC9AD5DF20A5B8557A5B</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:CE8B2EA6B80C1D0B7D54AFED44367CEC31069EBF</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2BCFE6D1DF5E9FB5A54D13913C85356F3CA0A640</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:99EE27D475386E73E268C661C8A4F430C7245557</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:B64D5099523AC2B97D4DAB9B5E7C081492E5097C</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:E2FA1B552EE4C2DA25256F572C11577482DF381D</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:9B148A677A66B76C4AA90367F0513A593BD43EBB</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2DB617FCC926F51F0E4DD9F131A0EABE416CE9C2</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:AB1356DC0D8F1BE6F0AB98FB658AF9D1E696EEC6</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:F7A7B8F83014A75B79B7666D42F4DB25CA5D054C</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:8AA301C9F7E205DB2E6E306CA20F30D880EF4CD3</t>
   </si>
   <si>
@@ -710,21 +293,9 @@
     <t>magnet:?xt=urn:btih:AAA884586F654E2E4DFE7E18C218A98504B4F843</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:E7AF6C342160D776D5AA57ED338E32EC4F3D5189</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:C132F7B1B21CFECD872AA0B2A7890258551FDCFA</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:5EA3F12E9EC6305B5519D4E8C3897E64987297EE</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:7F372943BE706C016943B971BEC2B815A3DC865A</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:550EE40C5D597B4F67C5B1402102BA982DDB1B69</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:2962D2BA0C8EAB29F87235DC20DC76915DF42E66</t>
   </si>
   <si>
@@ -734,9 +305,6 @@
     <t>magnet:?xt=urn:btih:1B81D01253A7ECB7B9185B596B6D5FBB36B1B914</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:34552F221625900E21CC129A698B48E0EE6B958A</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:924C75B384818A977B708E5764484D693B09E327</t>
   </si>
   <si>
@@ -746,49 +314,13 @@
     <t>magnet:?xt=urn:btih:E2D68C0D7286AC8381A9969F252863F137D7B060</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:95739914CCED08BE2FF7F771588EB2F4D85B43ED</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:A306F9B00651AD0BFD2BA89867287E19F0C72D15</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:832A1E3C963E9304D25D4CA8FB446A842B657598</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:48560B2A938062CAFC29241849549C9C406494AD</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:4F3411CC4611F3EA089FD8D0D165A0DAABDF2EA5</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:A45C9A2371BFBEE5F9ADA602025C4BC34E855F6D</t>
   </si>
   <si>
-    <t>magnet:?xt=urn:btih:123EBA14F6C02070DEEB24A51B677FF622452399</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:3A9AAEF2DAC4A701999E0E6DF9BC8A5735ACDA5C</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:0924492901C21DA1031EFC222C17BD8DB79CE9A3</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:8AB4AB0A7F97D8C9A2E179DA52924E98A4142D84</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:C98897CC74DB11F99F66CA5FA7384D7E12FF8F00</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:52A7C5B221ACDA81941559D8134C6A4523DE01F0</t>
-  </si>
-  <si>
     <t>magnet:?xt=urn:btih:8363230ABC6DE7F908A463C5C3AA744C13710BF8</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:4047341E4B5687D2F17F38CDDCB17873BBD22356</t>
-  </si>
-  <si>
-    <t>magnet:?xt=urn:btih:2D581CF208C97111A234B18E782F1674F966084E</t>
   </si>
   <si>
     <t>magnet:?xt=urn:btih:2D5DBA6A7076A1760EFA51B79B43F2714BB51418</t>
@@ -16188,8 +15720,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E5001"/>
+  <dimension ref="A1:E4845"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="67.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -40426,786 +39961,6 @@
     <row r="4845" s="1" customFormat="1" spans="1:1">
       <c r="A4845" s="2" t="s">
         <v>4848</v>
-      </c>
-    </row>
-    <row r="4846" s="1" customFormat="1" spans="1:1">
-      <c r="A4846" s="2" t="s">
-        <v>4849</v>
-      </c>
-    </row>
-    <row r="4847" s="1" customFormat="1" spans="1:1">
-      <c r="A4847" s="2" t="s">
-        <v>4850</v>
-      </c>
-    </row>
-    <row r="4848" s="1" customFormat="1" spans="1:1">
-      <c r="A4848" s="2" t="s">
-        <v>4851</v>
-      </c>
-    </row>
-    <row r="4849" s="1" customFormat="1" spans="1:1">
-      <c r="A4849" s="2" t="s">
-        <v>4852</v>
-      </c>
-    </row>
-    <row r="4850" s="1" customFormat="1" spans="1:1">
-      <c r="A4850" s="2" t="s">
-        <v>4853</v>
-      </c>
-    </row>
-    <row r="4851" s="1" customFormat="1" spans="1:1">
-      <c r="A4851" s="2" t="s">
-        <v>4854</v>
-      </c>
-    </row>
-    <row r="4852" s="1" customFormat="1" spans="1:1">
-      <c r="A4852" s="2" t="s">
-        <v>4855</v>
-      </c>
-    </row>
-    <row r="4853" s="1" customFormat="1" spans="1:1">
-      <c r="A4853" s="2" t="s">
-        <v>4856</v>
-      </c>
-    </row>
-    <row r="4854" s="1" customFormat="1" spans="1:1">
-      <c r="A4854" s="2" t="s">
-        <v>4857</v>
-      </c>
-    </row>
-    <row r="4855" s="1" customFormat="1" spans="1:1">
-      <c r="A4855" s="2" t="s">
-        <v>4858</v>
-      </c>
-    </row>
-    <row r="4856" s="1" customFormat="1" spans="1:1">
-      <c r="A4856" s="2" t="s">
-        <v>4859</v>
-      </c>
-    </row>
-    <row r="4857" s="1" customFormat="1" spans="1:1">
-      <c r="A4857" s="2" t="s">
-        <v>4860</v>
-      </c>
-    </row>
-    <row r="4858" s="1" customFormat="1" spans="1:1">
-      <c r="A4858" s="2" t="s">
-        <v>4861</v>
-      </c>
-    </row>
-    <row r="4859" s="1" customFormat="1" spans="1:1">
-      <c r="A4859" s="2" t="s">
-        <v>4862</v>
-      </c>
-    </row>
-    <row r="4860" s="1" customFormat="1" spans="1:1">
-      <c r="A4860" s="2" t="s">
-        <v>4863</v>
-      </c>
-    </row>
-    <row r="4861" s="1" customFormat="1" spans="1:1">
-      <c r="A4861" s="2" t="s">
-        <v>4864</v>
-      </c>
-    </row>
-    <row r="4862" s="1" customFormat="1" spans="1:1">
-      <c r="A4862" s="2" t="s">
-        <v>4865</v>
-      </c>
-    </row>
-    <row r="4863" s="1" customFormat="1" spans="1:1">
-      <c r="A4863" s="2" t="s">
-        <v>4866</v>
-      </c>
-    </row>
-    <row r="4864" s="1" customFormat="1" spans="1:1">
-      <c r="A4864" s="2" t="s">
-        <v>4867</v>
-      </c>
-    </row>
-    <row r="4865" s="1" customFormat="1" spans="1:1">
-      <c r="A4865" s="2" t="s">
-        <v>4868</v>
-      </c>
-    </row>
-    <row r="4866" s="1" customFormat="1" spans="1:1">
-      <c r="A4866" s="2" t="s">
-        <v>4869</v>
-      </c>
-    </row>
-    <row r="4867" s="1" customFormat="1" spans="1:1">
-      <c r="A4867" s="2" t="s">
-        <v>4870</v>
-      </c>
-    </row>
-    <row r="4868" s="1" customFormat="1" spans="1:1">
-      <c r="A4868" s="2" t="s">
-        <v>4871</v>
-      </c>
-    </row>
-    <row r="4869" s="1" customFormat="1" spans="1:1">
-      <c r="A4869" s="2" t="s">
-        <v>4872</v>
-      </c>
-    </row>
-    <row r="4870" s="1" customFormat="1" spans="1:1">
-      <c r="A4870" s="2" t="s">
-        <v>4873</v>
-      </c>
-    </row>
-    <row r="4871" s="1" customFormat="1" spans="1:1">
-      <c r="A4871" s="2" t="s">
-        <v>4874</v>
-      </c>
-    </row>
-    <row r="4872" s="1" customFormat="1" spans="1:1">
-      <c r="A4872" s="2" t="s">
-        <v>4875</v>
-      </c>
-    </row>
-    <row r="4873" s="1" customFormat="1" spans="1:1">
-      <c r="A4873" s="2" t="s">
-        <v>4876</v>
-      </c>
-    </row>
-    <row r="4874" s="1" customFormat="1" spans="1:1">
-      <c r="A4874" s="2" t="s">
-        <v>4877</v>
-      </c>
-    </row>
-    <row r="4875" s="1" customFormat="1" spans="1:1">
-      <c r="A4875" s="2" t="s">
-        <v>4878</v>
-      </c>
-    </row>
-    <row r="4876" s="1" customFormat="1" spans="1:1">
-      <c r="A4876" s="2" t="s">
-        <v>4879</v>
-      </c>
-    </row>
-    <row r="4877" s="1" customFormat="1" spans="1:1">
-      <c r="A4877" s="2" t="s">
-        <v>4880</v>
-      </c>
-    </row>
-    <row r="4878" s="1" customFormat="1" spans="1:1">
-      <c r="A4878" s="2" t="s">
-        <v>4881</v>
-      </c>
-    </row>
-    <row r="4879" s="1" customFormat="1" spans="1:1">
-      <c r="A4879" s="2" t="s">
-        <v>4882</v>
-      </c>
-    </row>
-    <row r="4880" s="1" customFormat="1" spans="1:1">
-      <c r="A4880" s="2" t="s">
-        <v>4883</v>
-      </c>
-    </row>
-    <row r="4881" s="1" customFormat="1" spans="1:1">
-      <c r="A4881" s="2" t="s">
-        <v>4884</v>
-      </c>
-    </row>
-    <row r="4882" s="1" customFormat="1" spans="1:1">
-      <c r="A4882" s="2" t="s">
-        <v>4885</v>
-      </c>
-    </row>
-    <row r="4883" s="1" customFormat="1" spans="1:1">
-      <c r="A4883" s="2" t="s">
-        <v>4886</v>
-      </c>
-    </row>
-    <row r="4884" s="1" customFormat="1" spans="1:1">
-      <c r="A4884" s="2" t="s">
-        <v>4887</v>
-      </c>
-    </row>
-    <row r="4885" s="1" customFormat="1" spans="1:1">
-      <c r="A4885" s="2" t="s">
-        <v>4888</v>
-      </c>
-    </row>
-    <row r="4886" s="1" customFormat="1" spans="1:1">
-      <c r="A4886" s="2" t="s">
-        <v>4889</v>
-      </c>
-    </row>
-    <row r="4887" s="1" customFormat="1" spans="1:1">
-      <c r="A4887" s="2" t="s">
-        <v>4890</v>
-      </c>
-    </row>
-    <row r="4888" s="1" customFormat="1" spans="1:1">
-      <c r="A4888" s="2" t="s">
-        <v>4891</v>
-      </c>
-    </row>
-    <row r="4889" s="1" customFormat="1" spans="1:1">
-      <c r="A4889" s="2" t="s">
-        <v>4892</v>
-      </c>
-    </row>
-    <row r="4890" s="1" customFormat="1" spans="1:1">
-      <c r="A4890" s="2" t="s">
-        <v>4893</v>
-      </c>
-    </row>
-    <row r="4891" s="1" customFormat="1" spans="1:1">
-      <c r="A4891" s="2" t="s">
-        <v>4894</v>
-      </c>
-    </row>
-    <row r="4892" s="1" customFormat="1" spans="1:1">
-      <c r="A4892" s="2" t="s">
-        <v>4895</v>
-      </c>
-    </row>
-    <row r="4893" s="1" customFormat="1" spans="1:1">
-      <c r="A4893" s="2" t="s">
-        <v>4896</v>
-      </c>
-    </row>
-    <row r="4894" s="1" customFormat="1" spans="1:1">
-      <c r="A4894" s="2" t="s">
-        <v>4897</v>
-      </c>
-    </row>
-    <row r="4895" s="1" customFormat="1" spans="1:1">
-      <c r="A4895" s="2" t="s">
-        <v>4898</v>
-      </c>
-    </row>
-    <row r="4896" s="1" customFormat="1" spans="1:1">
-      <c r="A4896" s="2" t="s">
-        <v>4899</v>
-      </c>
-    </row>
-    <row r="4897" s="1" customFormat="1" spans="1:1">
-      <c r="A4897" s="2" t="s">
-        <v>4900</v>
-      </c>
-    </row>
-    <row r="4898" s="1" customFormat="1" spans="1:1">
-      <c r="A4898" s="2" t="s">
-        <v>4901</v>
-      </c>
-    </row>
-    <row r="4899" s="1" customFormat="1" spans="1:1">
-      <c r="A4899" s="2" t="s">
-        <v>4902</v>
-      </c>
-    </row>
-    <row r="4900" s="1" customFormat="1" spans="1:1">
-      <c r="A4900" s="2" t="s">
-        <v>4903</v>
-      </c>
-    </row>
-    <row r="4901" s="1" customFormat="1" spans="1:1">
-      <c r="A4901" s="2" t="s">
-        <v>4904</v>
-      </c>
-    </row>
-    <row r="4902" s="1" customFormat="1" spans="1:1">
-      <c r="A4902" s="2" t="s">
-        <v>4905</v>
-      </c>
-    </row>
-    <row r="4903" s="1" customFormat="1" spans="1:1">
-      <c r="A4903" s="2" t="s">
-        <v>4906</v>
-      </c>
-    </row>
-    <row r="4904" s="1" customFormat="1" spans="1:1">
-      <c r="A4904" s="2" t="s">
-        <v>4907</v>
-      </c>
-    </row>
-    <row r="4905" s="1" customFormat="1" spans="1:1">
-      <c r="A4905" s="2" t="s">
-        <v>4908</v>
-      </c>
-    </row>
-    <row r="4906" s="1" customFormat="1" spans="1:1">
-      <c r="A4906" s="2" t="s">
-        <v>4909</v>
-      </c>
-    </row>
-    <row r="4907" s="1" customFormat="1" spans="1:1">
-      <c r="A4907" s="2" t="s">
-        <v>4910</v>
-      </c>
-    </row>
-    <row r="4908" s="1" customFormat="1" spans="1:1">
-      <c r="A4908" s="2" t="s">
-        <v>4911</v>
-      </c>
-    </row>
-    <row r="4909" s="1" customFormat="1" spans="1:1">
-      <c r="A4909" s="2" t="s">
-        <v>4912</v>
-      </c>
-    </row>
-    <row r="4910" s="1" customFormat="1" spans="1:1">
-      <c r="A4910" s="2" t="s">
-        <v>4913</v>
-      </c>
-    </row>
-    <row r="4911" s="1" customFormat="1" spans="1:1">
-      <c r="A4911" s="2" t="s">
-        <v>4914</v>
-      </c>
-    </row>
-    <row r="4912" s="1" customFormat="1" spans="1:1">
-      <c r="A4912" s="2" t="s">
-        <v>4915</v>
-      </c>
-    </row>
-    <row r="4913" s="1" customFormat="1" spans="1:1">
-      <c r="A4913" s="2" t="s">
-        <v>4916</v>
-      </c>
-    </row>
-    <row r="4914" s="1" customFormat="1" spans="1:1">
-      <c r="A4914" s="2" t="s">
-        <v>4917</v>
-      </c>
-    </row>
-    <row r="4915" s="1" customFormat="1" spans="1:1">
-      <c r="A4915" s="2" t="s">
-        <v>4918</v>
-      </c>
-    </row>
-    <row r="4916" s="1" customFormat="1" spans="1:1">
-      <c r="A4916" s="2" t="s">
-        <v>4919</v>
-      </c>
-    </row>
-    <row r="4917" s="1" customFormat="1" spans="1:1">
-      <c r="A4917" s="2" t="s">
-        <v>4920</v>
-      </c>
-    </row>
-    <row r="4918" s="1" customFormat="1" spans="1:1">
-      <c r="A4918" s="2" t="s">
-        <v>4921</v>
-      </c>
-    </row>
-    <row r="4919" s="1" customFormat="1" spans="1:1">
-      <c r="A4919" s="2" t="s">
-        <v>4922</v>
-      </c>
-    </row>
-    <row r="4920" s="1" customFormat="1" spans="1:1">
-      <c r="A4920" s="2" t="s">
-        <v>4923</v>
-      </c>
-    </row>
-    <row r="4921" s="1" customFormat="1" spans="1:1">
-      <c r="A4921" s="2" t="s">
-        <v>4924</v>
-      </c>
-    </row>
-    <row r="4922" s="1" customFormat="1" spans="1:1">
-      <c r="A4922" s="2" t="s">
-        <v>4925</v>
-      </c>
-    </row>
-    <row r="4923" s="1" customFormat="1" spans="1:1">
-      <c r="A4923" s="2" t="s">
-        <v>4926</v>
-      </c>
-    </row>
-    <row r="4924" s="1" customFormat="1" spans="1:1">
-      <c r="A4924" s="2" t="s">
-        <v>4927</v>
-      </c>
-    </row>
-    <row r="4925" s="1" customFormat="1" spans="1:1">
-      <c r="A4925" s="2" t="s">
-        <v>4928</v>
-      </c>
-    </row>
-    <row r="4926" s="1" customFormat="1" spans="1:1">
-      <c r="A4926" s="2" t="s">
-        <v>4929</v>
-      </c>
-    </row>
-    <row r="4927" s="1" customFormat="1" spans="1:1">
-      <c r="A4927" s="2" t="s">
-        <v>4930</v>
-      </c>
-    </row>
-    <row r="4928" s="1" customFormat="1" spans="1:1">
-      <c r="A4928" s="2" t="s">
-        <v>4931</v>
-      </c>
-    </row>
-    <row r="4929" s="1" customFormat="1" spans="1:1">
-      <c r="A4929" s="2" t="s">
-        <v>4932</v>
-      </c>
-    </row>
-    <row r="4930" s="1" customFormat="1" spans="1:1">
-      <c r="A4930" s="2" t="s">
-        <v>4933</v>
-      </c>
-    </row>
-    <row r="4931" s="1" customFormat="1" spans="1:1">
-      <c r="A4931" s="2" t="s">
-        <v>4934</v>
-      </c>
-    </row>
-    <row r="4932" s="1" customFormat="1" spans="1:1">
-      <c r="A4932" s="2" t="s">
-        <v>4935</v>
-      </c>
-    </row>
-    <row r="4933" s="1" customFormat="1" spans="1:1">
-      <c r="A4933" s="2" t="s">
-        <v>4936</v>
-      </c>
-    </row>
-    <row r="4934" s="1" customFormat="1" spans="1:1">
-      <c r="A4934" s="2" t="s">
-        <v>4937</v>
-      </c>
-    </row>
-    <row r="4935" s="1" customFormat="1" spans="1:1">
-      <c r="A4935" s="2" t="s">
-        <v>4938</v>
-      </c>
-    </row>
-    <row r="4936" s="1" customFormat="1" spans="1:1">
-      <c r="A4936" s="2" t="s">
-        <v>4939</v>
-      </c>
-    </row>
-    <row r="4937" s="1" customFormat="1" spans="1:1">
-      <c r="A4937" s="2" t="s">
-        <v>4940</v>
-      </c>
-    </row>
-    <row r="4938" s="1" customFormat="1" spans="1:1">
-      <c r="A4938" s="2" t="s">
-        <v>4941</v>
-      </c>
-    </row>
-    <row r="4939" s="1" customFormat="1" spans="1:1">
-      <c r="A4939" s="2" t="s">
-        <v>4942</v>
-      </c>
-    </row>
-    <row r="4940" s="1" customFormat="1" spans="1:1">
-      <c r="A4940" s="2" t="s">
-        <v>4943</v>
-      </c>
-    </row>
-    <row r="4941" s="1" customFormat="1" spans="1:1">
-      <c r="A4941" s="2" t="s">
-        <v>4944</v>
-      </c>
-    </row>
-    <row r="4942" s="1" customFormat="1" spans="1:1">
-      <c r="A4942" s="2" t="s">
-        <v>4945</v>
-      </c>
-    </row>
-    <row r="4943" s="1" customFormat="1" spans="1:1">
-      <c r="A4943" s="2" t="s">
-        <v>4946</v>
-      </c>
-    </row>
-    <row r="4944" s="1" customFormat="1" spans="1:1">
-      <c r="A4944" s="2" t="s">
-        <v>4947</v>
-      </c>
-    </row>
-    <row r="4945" s="1" customFormat="1" spans="1:1">
-      <c r="A4945" s="2" t="s">
-        <v>4948</v>
-      </c>
-    </row>
-    <row r="4946" s="1" customFormat="1" spans="1:1">
-      <c r="A4946" s="2" t="s">
-        <v>4949</v>
-      </c>
-    </row>
-    <row r="4947" s="1" customFormat="1" spans="1:1">
-      <c r="A4947" s="2" t="s">
-        <v>4950</v>
-      </c>
-    </row>
-    <row r="4948" s="1" customFormat="1" spans="1:1">
-      <c r="A4948" s="2" t="s">
-        <v>4951</v>
-      </c>
-    </row>
-    <row r="4949" s="1" customFormat="1" spans="1:1">
-      <c r="A4949" s="2" t="s">
-        <v>4952</v>
-      </c>
-    </row>
-    <row r="4950" s="1" customFormat="1" spans="1:1">
-      <c r="A4950" s="2" t="s">
-        <v>4953</v>
-      </c>
-    </row>
-    <row r="4951" s="1" customFormat="1" spans="1:1">
-      <c r="A4951" s="2" t="s">
-        <v>4954</v>
-      </c>
-    </row>
-    <row r="4952" s="1" customFormat="1" spans="1:1">
-      <c r="A4952" s="2" t="s">
-        <v>4955</v>
-      </c>
-    </row>
-    <row r="4953" s="1" customFormat="1" spans="1:1">
-      <c r="A4953" s="2" t="s">
-        <v>4956</v>
-      </c>
-    </row>
-    <row r="4954" s="1" customFormat="1" spans="1:1">
-      <c r="A4954" s="2" t="s">
-        <v>4957</v>
-      </c>
-    </row>
-    <row r="4955" s="1" customFormat="1" spans="1:1">
-      <c r="A4955" s="2" t="s">
-        <v>4958</v>
-      </c>
-    </row>
-    <row r="4956" s="1" customFormat="1" spans="1:1">
-      <c r="A4956" s="2" t="s">
-        <v>4959</v>
-      </c>
-    </row>
-    <row r="4957" s="1" customFormat="1" spans="1:1">
-      <c r="A4957" s="2" t="s">
-        <v>4960</v>
-      </c>
-    </row>
-    <row r="4958" s="1" customFormat="1" spans="1:1">
-      <c r="A4958" s="2" t="s">
-        <v>4961</v>
-      </c>
-    </row>
-    <row r="4959" s="1" customFormat="1" spans="1:1">
-      <c r="A4959" s="2" t="s">
-        <v>4962</v>
-      </c>
-    </row>
-    <row r="4960" s="1" customFormat="1" spans="1:1">
-      <c r="A4960" s="2" t="s">
-        <v>4963</v>
-      </c>
-    </row>
-    <row r="4961" s="1" customFormat="1" spans="1:1">
-      <c r="A4961" s="2" t="s">
-        <v>4964</v>
-      </c>
-    </row>
-    <row r="4962" s="1" customFormat="1" spans="1:1">
-      <c r="A4962" s="2" t="s">
-        <v>4965</v>
-      </c>
-    </row>
-    <row r="4963" s="1" customFormat="1" spans="1:1">
-      <c r="A4963" s="2" t="s">
-        <v>4966</v>
-      </c>
-    </row>
-    <row r="4964" s="1" customFormat="1" spans="1:1">
-      <c r="A4964" s="2" t="s">
-        <v>4967</v>
-      </c>
-    </row>
-    <row r="4965" s="1" customFormat="1" spans="1:1">
-      <c r="A4965" s="2" t="s">
-        <v>4968</v>
-      </c>
-    </row>
-    <row r="4966" s="1" customFormat="1" spans="1:1">
-      <c r="A4966" s="2" t="s">
-        <v>4969</v>
-      </c>
-    </row>
-    <row r="4967" s="1" customFormat="1" spans="1:1">
-      <c r="A4967" s="2" t="s">
-        <v>4970</v>
-      </c>
-    </row>
-    <row r="4968" s="1" customFormat="1" spans="1:1">
-      <c r="A4968" s="2" t="s">
-        <v>4971</v>
-      </c>
-    </row>
-    <row r="4969" s="1" customFormat="1" spans="1:1">
-      <c r="A4969" s="2" t="s">
-        <v>4972</v>
-      </c>
-    </row>
-    <row r="4970" s="1" customFormat="1" spans="1:1">
-      <c r="A4970" s="2" t="s">
-        <v>4973</v>
-      </c>
-    </row>
-    <row r="4971" s="1" customFormat="1" spans="1:1">
-      <c r="A4971" s="2" t="s">
-        <v>4974</v>
-      </c>
-    </row>
-    <row r="4972" s="1" customFormat="1" spans="1:1">
-      <c r="A4972" s="2" t="s">
-        <v>4975</v>
-      </c>
-    </row>
-    <row r="4973" s="1" customFormat="1" spans="1:1">
-      <c r="A4973" s="2" t="s">
-        <v>4976</v>
-      </c>
-    </row>
-    <row r="4974" s="1" customFormat="1" spans="1:1">
-      <c r="A4974" s="2" t="s">
-        <v>4977</v>
-      </c>
-    </row>
-    <row r="4975" s="1" customFormat="1" spans="1:1">
-      <c r="A4975" s="2" t="s">
-        <v>4978</v>
-      </c>
-    </row>
-    <row r="4976" s="1" customFormat="1" spans="1:1">
-      <c r="A4976" s="2" t="s">
-        <v>4979</v>
-      </c>
-    </row>
-    <row r="4977" s="1" customFormat="1" spans="1:1">
-      <c r="A4977" s="2" t="s">
-        <v>4980</v>
-      </c>
-    </row>
-    <row r="4978" s="1" customFormat="1" spans="1:1">
-      <c r="A4978" s="2" t="s">
-        <v>4981</v>
-      </c>
-    </row>
-    <row r="4979" s="1" customFormat="1" spans="1:1">
-      <c r="A4979" s="2" t="s">
-        <v>4982</v>
-      </c>
-    </row>
-    <row r="4980" s="1" customFormat="1" spans="1:1">
-      <c r="A4980" s="2" t="s">
-        <v>4983</v>
-      </c>
-    </row>
-    <row r="4981" s="1" customFormat="1" spans="1:1">
-      <c r="A4981" s="2" t="s">
-        <v>4984</v>
-      </c>
-    </row>
-    <row r="4982" s="1" customFormat="1" spans="1:1">
-      <c r="A4982" s="2" t="s">
-        <v>4985</v>
-      </c>
-    </row>
-    <row r="4983" s="1" customFormat="1" spans="1:1">
-      <c r="A4983" s="2" t="s">
-        <v>4986</v>
-      </c>
-    </row>
-    <row r="4984" s="1" customFormat="1" spans="1:1">
-      <c r="A4984" s="2" t="s">
-        <v>4987</v>
-      </c>
-    </row>
-    <row r="4985" s="1" customFormat="1" spans="1:1">
-      <c r="A4985" s="2" t="s">
-        <v>4988</v>
-      </c>
-    </row>
-    <row r="4986" s="1" customFormat="1" spans="1:1">
-      <c r="A4986" s="2" t="s">
-        <v>4989</v>
-      </c>
-    </row>
-    <row r="4987" s="1" customFormat="1" spans="1:1">
-      <c r="A4987" s="2" t="s">
-        <v>4990</v>
-      </c>
-    </row>
-    <row r="4988" s="1" customFormat="1" spans="1:1">
-      <c r="A4988" s="2" t="s">
-        <v>4991</v>
-      </c>
-    </row>
-    <row r="4989" s="1" customFormat="1" spans="1:1">
-      <c r="A4989" s="2" t="s">
-        <v>4992</v>
-      </c>
-    </row>
-    <row r="4990" s="1" customFormat="1" spans="1:1">
-      <c r="A4990" s="2" t="s">
-        <v>4993</v>
-      </c>
-    </row>
-    <row r="4991" s="1" customFormat="1" spans="1:1">
-      <c r="A4991" s="2" t="s">
-        <v>4994</v>
-      </c>
-    </row>
-    <row r="4992" s="1" customFormat="1" spans="1:1">
-      <c r="A4992" s="2" t="s">
-        <v>4995</v>
-      </c>
-    </row>
-    <row r="4993" s="1" customFormat="1" spans="1:1">
-      <c r="A4993" s="2" t="s">
-        <v>4996</v>
-      </c>
-    </row>
-    <row r="4994" s="1" customFormat="1" spans="1:1">
-      <c r="A4994" s="2" t="s">
-        <v>4997</v>
-      </c>
-    </row>
-    <row r="4995" s="1" customFormat="1" spans="1:1">
-      <c r="A4995" s="2" t="s">
-        <v>4998</v>
-      </c>
-    </row>
-    <row r="4996" s="1" customFormat="1" spans="1:1">
-      <c r="A4996" s="2" t="s">
-        <v>4999</v>
-      </c>
-    </row>
-    <row r="4997" s="1" customFormat="1" spans="1:1">
-      <c r="A4997" s="2" t="s">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="4998" s="1" customFormat="1" spans="1:1">
-      <c r="A4998" s="2" t="s">
-        <v>5001</v>
-      </c>
-    </row>
-    <row r="4999" s="1" customFormat="1" spans="1:1">
-      <c r="A4999" s="2" t="s">
-        <v>5002</v>
-      </c>
-    </row>
-    <row r="5000" s="1" customFormat="1" spans="1:1">
-      <c r="A5000" s="2" t="s">
-        <v>5003</v>
-      </c>
-    </row>
-    <row r="5001" s="1" customFormat="1" spans="1:1">
-      <c r="A5001" s="2" t="s">
-        <v>5004</v>
       </c>
     </row>
   </sheetData>
